--- a/excel-files/NAVOTAS/DAANGHARI ELEMENTARY SCHOOL.xlsx
+++ b/excel-files/NAVOTAS/DAANGHARI ELEMENTARY SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29704"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29917"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="153" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE27F43D-12EC-4CEC-A10B-005318F1BBC6}"/>
+  <xr:revisionPtr revIDLastSave="284" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB063AB4-2006-49F3-BB2C-FEBBE3A25F30}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="92">
   <si>
     <t>Grade Level</t>
   </si>
@@ -82,6 +82,9 @@
     <t>Math</t>
   </si>
   <si>
+    <t>CO</t>
+  </si>
+  <si>
     <t>Science</t>
   </si>
   <si>
@@ -89,9 +92,6 @@
   </si>
   <si>
     <t>Filipino</t>
-  </si>
-  <si>
-    <t>CO</t>
   </si>
   <si>
     <t>Araling Panlipunan</t>
@@ -3714,17 +3714,25 @@
       <c r="B11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="5"/>
+      <c r="C11" s="1">
+        <v>176</v>
+      </c>
+      <c r="D11" s="1">
+        <v>220</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G11" s="3">
         <f>IF((C11-D11)&lt;0,0,C11-D11)</f>
         <v>0</v>
       </c>
       <c r="H11" s="4">
         <f>IF((D11-C11)&lt;0,0,D11-C11)</f>
-        <v>0</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="19.149999999999999">
@@ -3817,7 +3825,7 @@
         <v>3</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -3887,7 +3895,7 @@
         <v>4</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
@@ -3907,7 +3915,7 @@
         <v>4</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C22" s="1">
         <v>191</v>
@@ -3919,7 +3927,7 @@
         <v>2025</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G22" s="3">
         <f t="shared" si="4"/>
@@ -3947,7 +3955,7 @@
         <v>2025</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G23" s="3">
         <f t="shared" si="4"/>
@@ -3975,7 +3983,7 @@
         <v>2025</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G24" s="3">
         <f t="shared" si="4"/>
@@ -3993,17 +4001,25 @@
       <c r="B25" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="5"/>
+      <c r="C25" s="1">
+        <v>191</v>
+      </c>
+      <c r="D25" s="1">
+        <v>271</v>
+      </c>
+      <c r="E25" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G25" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H25" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="33.75" customHeight="1">
@@ -4011,19 +4027,27 @@
         <v>4</v>
       </c>
       <c r="B26" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="1">
+        <v>191</v>
+      </c>
+      <c r="D26" s="1">
+        <v>271</v>
+      </c>
+      <c r="E26" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F26" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="5"/>
       <c r="G26" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H26" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="33.75" customHeight="1">
@@ -4033,17 +4057,25 @@
       <c r="B27" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="5"/>
+      <c r="C27" s="1">
+        <v>191</v>
+      </c>
+      <c r="D27" s="1">
+        <v>271</v>
+      </c>
+      <c r="E27" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G27" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H27" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="27.75" customHeight="1">
@@ -4073,17 +4105,25 @@
       <c r="B29" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="5"/>
+      <c r="C29" s="1">
+        <v>191</v>
+      </c>
+      <c r="D29" s="1">
+        <v>271</v>
+      </c>
+      <c r="E29" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G29" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H29" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="27.75" customHeight="1">
@@ -4101,19 +4141,27 @@
         <v>5</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="5"/>
+        <v>16</v>
+      </c>
+      <c r="C31" s="1">
+        <v>199</v>
+      </c>
+      <c r="D31" s="1">
+        <v>248</v>
+      </c>
+      <c r="E31" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G31" s="3">
         <f t="shared" ref="G31:G39" si="6">IF((C31-D31)&lt;0,0,C31-D31)</f>
         <v>0</v>
       </c>
       <c r="H31" s="4">
         <f t="shared" ref="H31:H39" si="7">IF((D31-C31)&lt;0,0,D31-C31)</f>
-        <v>0</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="27.75" customHeight="1">
@@ -4121,7 +4169,7 @@
         <v>5</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
@@ -4193,7 +4241,7 @@
         <v>2025</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G35" s="3">
         <f t="shared" si="6"/>
@@ -4209,19 +4257,27 @@
         <v>5</v>
       </c>
       <c r="B36" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C36" s="1">
+        <v>199</v>
+      </c>
+      <c r="D36" s="1">
+        <v>248</v>
+      </c>
+      <c r="E36" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F36" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="5"/>
       <c r="G36" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H36" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="27.75" customHeight="1">
@@ -4241,7 +4297,7 @@
         <v>2025</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G37" s="3">
         <f t="shared" si="6"/>
@@ -4259,17 +4315,25 @@
       <c r="B38" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="5"/>
+      <c r="C38" s="1">
+        <v>199</v>
+      </c>
+      <c r="D38" s="1">
+        <v>248</v>
+      </c>
+      <c r="E38" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G38" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H38" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>49</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="27.75" customHeight="1">
@@ -4307,7 +4371,7 @@
         <v>6</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
@@ -4327,7 +4391,7 @@
         <v>6</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
@@ -4407,7 +4471,7 @@
         <v>6</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
@@ -4497,7 +4561,7 @@
         <v>7</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="10"/>
@@ -4517,7 +4581,7 @@
         <v>7</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C52" s="10"/>
       <c r="D52" s="10"/>
@@ -4597,7 +4661,7 @@
         <v>7</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C56" s="10"/>
       <c r="D56" s="10"/>
@@ -4687,7 +4751,7 @@
         <v>8</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="10"/>
@@ -4707,7 +4771,7 @@
         <v>8</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C62" s="10"/>
       <c r="D62" s="10"/>
@@ -4787,7 +4851,7 @@
         <v>8</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C66" s="10"/>
       <c r="D66" s="10"/>
@@ -4877,7 +4941,7 @@
         <v>9</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="10"/>
@@ -4897,7 +4961,7 @@
         <v>9</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C72" s="10"/>
       <c r="D72" s="10"/>
@@ -4977,7 +5041,7 @@
         <v>9</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C76" s="10"/>
       <c r="D76" s="10"/>
@@ -5067,7 +5131,7 @@
         <v>10</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="10"/>
@@ -5087,7 +5151,7 @@
         <v>10</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C82" s="10"/>
       <c r="D82" s="10"/>
@@ -5167,7 +5231,7 @@
         <v>10</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C86" s="10"/>
       <c r="D86" s="10"/>
@@ -5419,10 +5483,10 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E2:E6 E8:E12 E14:E19 E81:E89 E21:E29 E41:E49 E51:E59 E61:E69 E71:E79 E31:E39" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025 ,2026"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F91:F98 F21:F29 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F31:F39" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5435,7 +5499,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -6010,7 +6074,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="5">
@@ -6079,7 +6143,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="5">
@@ -6611,7 +6675,7 @@
         <v>2</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C19" s="1">
         <v>173</v>
@@ -6694,7 +6758,7 @@
         <v>2</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C20" s="1">
         <v>173</v>
@@ -7075,7 +7139,7 @@
         <v>3</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C26" s="1">
         <v>206</v>
@@ -7306,7 +7370,7 @@
         <v>3</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C29" s="1">
         <v>206</v>
@@ -7383,7 +7447,7 @@
         <v>3</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C30" s="1">
         <v>206</v>
@@ -7543,7 +7607,7 @@
         <v>4</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="5">
@@ -7612,7 +7676,7 @@
         <v>4</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="5">
@@ -7888,7 +7952,7 @@
         <v>4</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="5">
@@ -8178,7 +8242,7 @@
         <v>5</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C43" s="5">
         <v>199</v>
@@ -8261,7 +8325,7 @@
         <v>5</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C44" s="5">
         <v>199</v>
@@ -8575,7 +8639,7 @@
         <v>5</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C48" s="5">
         <v>199</v>
@@ -8897,7 +8961,7 @@
         <v>6</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="5">
@@ -8966,7 +9030,7 @@
         <v>6</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C54" s="1"/>
       <c r="D54" s="5">
@@ -9242,7 +9306,7 @@
         <v>6</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="5">
@@ -9532,7 +9596,7 @@
         <v>7</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="12">
@@ -9601,7 +9665,7 @@
         <v>7</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C64" s="10"/>
       <c r="D64" s="12">
@@ -9877,7 +9941,7 @@
         <v>7</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C68" s="10"/>
       <c r="D68" s="12">
@@ -10167,7 +10231,7 @@
         <v>8</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="12">
@@ -10236,7 +10300,7 @@
         <v>8</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C74" s="10"/>
       <c r="D74" s="12">
@@ -10512,7 +10576,7 @@
         <v>8</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C78" s="10"/>
       <c r="D78" s="12">
@@ -10802,7 +10866,7 @@
         <v>9</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="12">
@@ -10871,7 +10935,7 @@
         <v>9</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C84" s="10"/>
       <c r="D84" s="12">
@@ -11147,7 +11211,7 @@
         <v>9</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C88" s="10"/>
       <c r="D88" s="12">
@@ -11437,7 +11501,7 @@
         <v>10</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="12">
@@ -11506,7 +11570,7 @@
         <v>10</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C94" s="10"/>
       <c r="D94" s="12">
@@ -11782,7 +11846,7 @@
         <v>10</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C98" s="10"/>
       <c r="D98" s="12">
@@ -13617,186 +13681,6 @@
       <c r="AA127" s="5">
         <f t="shared" si="21"/>
         <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
       </c>
     </row>
   </sheetData>
@@ -13816,8 +13700,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 F43:F51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 F14:F21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 L14:L21 F33:F41 F23:F31 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 X112:X127 F103:F110 R103:R110 L103:L110 X103:X110 L43:L51" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X112:X127 F5:F12 F14:F21 F23:F31 F33:F41 F43:F51 F53:F61 F63:F71 F73:F81 F83:F91 F93:F101 F103:F110 F112:F127 L5:L12 L14:L21 L23:L31 L33:L41 L43:L51 L53:L61 L63:L71 L73:L81 L83:L91 L93:L101 L103:L110 L112:L127 R5:R12 R14:R21 R23:R31 R33:R41 R43:R51 R53:R61 R63:R71 R73:R81 R83:R91 R93:R101 R103:R110 R112:R127 X5:X12 X14:X21 X23:X31 X33:X41 X43:X51 X53:X61 X63:X71 X73:X81 X83:X91 X93:X101 X103:X110" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025 ,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G14:G21 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G103:G110 G43:G51 G33:G41 G23:G31 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 M14:M110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
@@ -13835,7 +13719,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB170"/>
+  <dimension ref="A1:AB140"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -14331,7 +14215,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="5">
@@ -14400,7 +14284,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="5">
@@ -14884,7 +14768,7 @@
         <v>2</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="5">
@@ -14953,7 +14837,7 @@
         <v>2</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="5">
@@ -15299,7 +15183,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="5">
@@ -15506,7 +15390,7 @@
         <v>3</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="5">
@@ -15575,7 +15459,7 @@
         <v>3</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="5">
@@ -15714,7 +15598,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="5">
@@ -15783,7 +15667,7 @@
         <v>4</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="5">
@@ -16059,7 +15943,7 @@
         <v>4</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="5">
@@ -16474,7 +16358,7 @@
         <v>5</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="5">
@@ -16543,7 +16427,7 @@
         <v>5</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="5">
@@ -16819,7 +16703,7 @@
         <v>5</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="5">
@@ -17234,7 +17118,7 @@
         <v>6</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C55" s="1">
         <v>172</v>
@@ -17329,7 +17213,7 @@
         <v>6</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C56" s="1">
         <v>172</v>
@@ -17685,7 +17569,7 @@
         <v>6</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C60" s="1">
         <v>172</v>
@@ -18170,7 +18054,7 @@
         <v>7</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="12">
@@ -18239,7 +18123,7 @@
         <v>7</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C68" s="10"/>
       <c r="D68" s="12">
@@ -18515,7 +18399,7 @@
         <v>7</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C72" s="10"/>
       <c r="D72" s="12">
@@ -18930,7 +18814,7 @@
         <v>8</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="12">
@@ -18999,7 +18883,7 @@
         <v>8</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C80" s="10"/>
       <c r="D80" s="12">
@@ -19275,7 +19159,7 @@
         <v>8</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C84" s="10"/>
       <c r="D84" s="12">
@@ -19690,7 +19574,7 @@
         <v>9</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="12">
@@ -19759,7 +19643,7 @@
         <v>9</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C92" s="10"/>
       <c r="D92" s="12">
@@ -20035,7 +19919,7 @@
         <v>9</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C96" s="10"/>
       <c r="D96" s="12">
@@ -20450,7 +20334,7 @@
         <v>10</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="12">
@@ -20519,7 +20403,7 @@
         <v>10</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C104" s="10"/>
       <c r="D104" s="12">
@@ -20795,7 +20679,7 @@
         <v>10</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C108" s="10"/>
       <c r="D108" s="12">
@@ -22268,186 +22152,6 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101" name="Textbooks"/>
@@ -22465,8 +22169,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 M115:M122 S55:S65 M55:M65 G55:G65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 Y55:Y65" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 R55:R65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 F103:F113 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 X55:X65" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X115:X122 F3:F10 F12:F19 F21:F29 F31:F41 F43:F53 F55:F65 F67:F77 F79:F89 F91:F101 F103:F113 F115:F122 L3:L10 L12:L19 L21:L29 L31:L41 L43:L53 L55:L65 L67:L77 L79:L89 L91:L101 L103:L113 L115:L122 R3:R10 R12:R19 R21:R29 R31:R41 R43:R53 R55:R65 R67:R77 R79:R89 R91:R101 R103:R113 R115:R122 X3:X10 X12:X19 X21:X29 X31:X41 X43:X53 X55:X65 X67:X77 X79:X89 X91:X101 X103:X113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025 ,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
